--- a/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023</t>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,58</t>
+          <t>1,21; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,3</t>
+          <t>0,7; 4,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,81</t>
+          <t>1,25; 3,85</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,26</t>
+          <t>1,37; 6,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,44</t>
+          <t>1,07; 5,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,68</t>
+          <t>1,64; 4,55</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,32</t>
+          <t>0,61; 3,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,5</t>
+          <t>0,55; 3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,72</t>
+          <t>0,8; 2,65</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,34</t>
+          <t>1,39; 3,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,82</t>
+          <t>1,08; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,67</t>
+          <t>1,42; 2,69</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2021</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1956</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1925; 8421</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1274; 7976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4277; 13173</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5561</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5645</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11206</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2377; 10895</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2266; 10888</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6318; 17549</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1688; 9573</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1675; 10468</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4656; 15387</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9220; 22171</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8264; 21555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20251; 38405</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,29</t>
+          <t>1,27; 5,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,37</t>
+          <t>0,69; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,85</t>
+          <t>1,32; 3,71</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,3</t>
+          <t>1,42; 6,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,12</t>
+          <t>1,0; 5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,55</t>
+          <t>1,65; 4,89</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,48</t>
+          <t>0,59; 3,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,43</t>
+          <t>0,51; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,65</t>
+          <t>0,71; 2,58</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,33</t>
+          <t>1,43; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,83</t>
+          <t>1,03; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,69</t>
+          <t>1,42; 2,68</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>0; 2199</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1956</t>
+          <t>0; 2133</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1925; 8421</t>
+          <t>2021; 8976</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1274; 7976</t>
+          <t>1254; 7477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4277; 13173</t>
+          <t>4515; 12677</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2377; 10895</t>
+          <t>2453; 11115</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2266; 10888</t>
+          <t>2135; 11085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6318; 17549</t>
+          <t>6380; 18839</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1688; 9573</t>
+          <t>1627; 9010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1675; 10468</t>
+          <t>1548; 10420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4656; 15387</t>
+          <t>4147; 15003</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9220; 22171</t>
+          <t>9523; 21824</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8264; 21555</t>
+          <t>7886; 21745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20251; 38405</t>
+          <t>20271; 38237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,63</t>
+          <t>0,79; 4,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,1</t>
+          <t>1,35; 5,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,71</t>
+          <t>1,39; 4,06</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,42</t>
+          <t>1,24; 5,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,22</t>
+          <t>1,36; 6,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,89</t>
+          <t>1,74; 4,76</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,27</t>
+          <t>0,52; 3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,41</t>
+          <t>0,76; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,58</t>
+          <t>0,86; 2,95</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,28</t>
+          <t>1,14; 2,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,85</t>
+          <t>1,5; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,68</t>
+          <t>1,49; 2,84</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>340</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2199</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1663</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2133</t>
+          <t>0; 1730</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7306</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2021; 8976</t>
+          <t>1250; 7125</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1254; 7477</t>
+          <t>1960; 8551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4515; 12677</t>
+          <t>4211; 12308</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11141</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2453; 11115</t>
+          <t>2473; 11507</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2135; 11085</t>
+          <t>2372; 11297</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6380; 18839</t>
+          <t>6521; 17833</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8998</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1627; 9010</t>
+          <t>1535; 10401</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1548; 10420</t>
+          <t>1954; 9710</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4147; 15003</t>
+          <t>4738; 16179</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9523; 21824</t>
+          <t>7972; 20665</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7886; 21745</t>
+          <t>9434; 22381</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20271; 38237</t>
+          <t>19773; 37784</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,79; 4,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 5,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 4,06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 5,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 6,47</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,74; 4,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 3,55</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 3,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 2,95</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 3,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 2,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.006532570790092704</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.003315682605291968</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1663</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1730</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.03193121633590865</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.016855783168069</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.0193639746591434</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.02924667544234994</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02410959124836346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3050</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7306</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.007933233254303734</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01347005246777532</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01389427235985618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1250; 7125</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1960; 8551</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4211; 12308</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04523296498340739</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.05876433230514255</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.04061563337242105</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02801618745861694</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.0316838159655886</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.0297254624372238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5607</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11141</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.01235575675187212</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01357700064426488</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01739950396843565</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2473; 11507</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2372; 11297</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6521; 17833</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05749771505374535</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06467791498791808</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.04758139938947903</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01527283478366655</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01765008843308339</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01638334930321596</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4528</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.005244526059862249</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.007615972137772528</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.008627949423997843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1535; 10401</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1954; 9710</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4738; 16179</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.03554076005157388</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.03784974581998964</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02945898738432674</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +768,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01872997507157947</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02331090184581332</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.02089641777762587</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>14659</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27785</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.01137457475397697</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.01500279473365131</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01487034949691942</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>7972; 20665</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9434; 22381</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19773; 37784</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02948654580432733</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.03559112718174554</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02841607912489146</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +833,445 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>340</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>1663</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>4256</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7306</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1960</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>7125</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>8551</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12308</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>5607</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5534</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>11141</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>2473</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2372</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>6521</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>11507</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11297</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>17833</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4470</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>4528</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>8998</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1535</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1954</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>10401</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>9710</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>16179</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>13127</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>14659</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>27785</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>7972</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>9434</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>19773</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>20665</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>22381</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>37784</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>